--- a/artfynd/A 3594-2026 artfynd.xlsx
+++ b/artfynd/A 3594-2026 artfynd.xlsx
@@ -902,7 +902,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131194295</v>
+        <v>131194294</v>
       </c>
       <c r="B4" t="n">
         <v>57884</v>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598150</v>
+        <v>598165</v>
       </c>
       <c r="R4" t="n">
-        <v>6942312</v>
+        <v>6942308</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,7 +1022,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131194294</v>
+        <v>131194295</v>
       </c>
       <c r="B5" t="n">
         <v>57884</v>
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598165</v>
+        <v>598150</v>
       </c>
       <c r="R5" t="n">
-        <v>6942308</v>
+        <v>6942312</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 3594-2026 artfynd.xlsx
+++ b/artfynd/A 3594-2026 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>131194297</v>
       </c>
       <c r="B3" t="n">
-        <v>79243</v>
+        <v>79244</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 3594-2026 artfynd.xlsx
+++ b/artfynd/A 3594-2026 artfynd.xlsx
@@ -902,7 +902,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131194294</v>
+        <v>131194295</v>
       </c>
       <c r="B4" t="n">
         <v>57884</v>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598165</v>
+        <v>598150</v>
       </c>
       <c r="R4" t="n">
-        <v>6942308</v>
+        <v>6942312</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,7 +1022,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131194295</v>
+        <v>131194294</v>
       </c>
       <c r="B5" t="n">
         <v>57884</v>
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598150</v>
+        <v>598165</v>
       </c>
       <c r="R5" t="n">
-        <v>6942312</v>
+        <v>6942308</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 3594-2026 artfynd.xlsx
+++ b/artfynd/A 3594-2026 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>131194297</v>
       </c>
       <c r="B3" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131194295</v>
+        <v>131194294</v>
       </c>
       <c r="B4" t="n">
         <v>57884</v>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598150</v>
+        <v>598165</v>
       </c>
       <c r="R4" t="n">
-        <v>6942312</v>
+        <v>6942308</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,7 +1022,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131194294</v>
+        <v>131194295</v>
       </c>
       <c r="B5" t="n">
         <v>57884</v>
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598165</v>
+        <v>598150</v>
       </c>
       <c r="R5" t="n">
-        <v>6942308</v>
+        <v>6942312</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 3594-2026 artfynd.xlsx
+++ b/artfynd/A 3594-2026 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>131194297</v>
       </c>
       <c r="B3" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 3594-2026 artfynd.xlsx
+++ b/artfynd/A 3594-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131194296</v>
       </c>
       <c r="B2" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>131194297</v>
       </c>
       <c r="B3" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>131194294</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>131194295</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>131194299</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>131194298</v>
       </c>
       <c r="B7" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 3594-2026 artfynd.xlsx
+++ b/artfynd/A 3594-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131194296</v>
       </c>
       <c r="B2" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>131194297</v>
       </c>
       <c r="B3" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>131194294</v>
       </c>
       <c r="B4" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>131194295</v>
       </c>
       <c r="B5" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>131194299</v>
       </c>
       <c r="B6" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>131194298</v>
       </c>
       <c r="B7" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 3594-2026 artfynd.xlsx
+++ b/artfynd/A 3594-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131194296</v>
       </c>
       <c r="B2" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>131194297</v>
       </c>
       <c r="B3" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131194294</v>
+        <v>131194295</v>
       </c>
       <c r="B4" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598165</v>
+        <v>598150</v>
       </c>
       <c r="R4" t="n">
-        <v>6942308</v>
+        <v>6942312</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,10 +1022,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131194295</v>
+        <v>131194294</v>
       </c>
       <c r="B5" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598150</v>
+        <v>598165</v>
       </c>
       <c r="R5" t="n">
-        <v>6942312</v>
+        <v>6942308</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,7 +1145,7 @@
         <v>131194299</v>
       </c>
       <c r="B6" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>131194298</v>
       </c>
       <c r="B7" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 3594-2026 artfynd.xlsx
+++ b/artfynd/A 3594-2026 artfynd.xlsx
@@ -902,7 +902,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131194295</v>
+        <v>131194294</v>
       </c>
       <c r="B4" t="n">
         <v>57888</v>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598150</v>
+        <v>598165</v>
       </c>
       <c r="R4" t="n">
-        <v>6942312</v>
+        <v>6942308</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,7 +1022,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131194294</v>
+        <v>131194295</v>
       </c>
       <c r="B5" t="n">
         <v>57888</v>
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598165</v>
+        <v>598150</v>
       </c>
       <c r="R5" t="n">
-        <v>6942308</v>
+        <v>6942312</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 3594-2026 artfynd.xlsx
+++ b/artfynd/A 3594-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131194296</v>
       </c>
       <c r="B2" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>131194297</v>
       </c>
       <c r="B3" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>131194294</v>
       </c>
       <c r="B4" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>131194295</v>
       </c>
       <c r="B5" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>131194299</v>
       </c>
       <c r="B6" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>131194298</v>
       </c>
       <c r="B7" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 3594-2026 artfynd.xlsx
+++ b/artfynd/A 3594-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131194296</v>
       </c>
       <c r="B2" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>131194297</v>
       </c>
       <c r="B3" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>131194294</v>
       </c>
       <c r="B4" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>131194295</v>
       </c>
       <c r="B5" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>131194299</v>
       </c>
       <c r="B6" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>131194298</v>
       </c>
       <c r="B7" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 3594-2026 artfynd.xlsx
+++ b/artfynd/A 3594-2026 artfynd.xlsx
@@ -675,53 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131194296</v>
+        <v>131194297</v>
       </c>
       <c r="B2" t="n">
-        <v>57898</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Starrmyran, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598143</v>
+        <v>598136</v>
       </c>
       <c r="R2" t="n">
-        <v>6942298</v>
+        <v>6942315</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,19 +755,14 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:23</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Flera påbörjade bohål i död gran. Ca 3 meter ovan mark och uppåt. Sannolikt tretåig hackspett. I en för arten lämplig biotop, med gott om stående död ved och många barrträd med färska ringhack i närheten.</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
@@ -795,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131194297</v>
+        <v>131194294</v>
       </c>
       <c r="B3" t="n">
-        <v>79260</v>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,34 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Starrmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598136</v>
+        <v>598165</v>
       </c>
       <c r="R3" t="n">
-        <v>6942315</v>
+        <v>6942308</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,7 +870,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:27</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131194294</v>
+        <v>131194295</v>
       </c>
       <c r="B4" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598165</v>
+        <v>598150</v>
       </c>
       <c r="R4" t="n">
-        <v>6942308</v>
+        <v>6942312</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,10 +1022,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131194295</v>
+        <v>131194296</v>
       </c>
       <c r="B5" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598150</v>
+        <v>598143</v>
       </c>
       <c r="R5" t="n">
-        <v>6942312</v>
+        <v>6942298</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,19 +1110,19 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>Flera påbörjade bohål i död gran. Ca 3 meter ovan mark och uppåt. Sannolikt tretåig hackspett. I en för arten lämplig biotop, med gott om stående död ved och många barrträd med färska ringhack i närheten.</t>
         </is>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG5" t="b">
         <v>0</v>
@@ -1142,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131194299</v>
+        <v>131194298</v>
       </c>
       <c r="B6" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>598154</v>
+        <v>598134</v>
       </c>
       <c r="R6" t="n">
-        <v>6942265</v>
+        <v>6942267</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1262,10 +1262,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131194298</v>
+        <v>131194299</v>
       </c>
       <c r="B7" t="n">
-        <v>57898</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>598134</v>
+        <v>598154</v>
       </c>
       <c r="R7" t="n">
-        <v>6942267</v>
+        <v>6942265</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">

--- a/artfynd/A 3594-2026 artfynd.xlsx
+++ b/artfynd/A 3594-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194297</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194294</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1019,6 +1034,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194295</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1139,6 +1159,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194296</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1259,6 +1284,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194298</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1379,8 +1409,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131194299</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>